--- a/0_Document/업그레이드.xlsx
+++ b/0_Document/업그레이드.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Adventure\Assets\0_Adventure\Deploy\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\Game Porject\Project LinkDeploy\0_Document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA82D816-9F22-42D9-8F78-1B223D7AB50C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F196EA44-83F1-494B-964D-385713554585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="40">
   <si>
     <t>Type</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -39,14 +39,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>StoneFactory</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ArrowFactory</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>AmmoFactory</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -59,14 +51,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>FactoryBuff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TowerBuff</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Tower</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -107,69 +91,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>버프 %증가</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>대미지 증가</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Hall</t>
-  </si>
-  <si>
-    <t>Hall</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>총알 공장 X 3, 도로 X 15, 총 X1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>공장 버프 X3, 타워버프 X2, 총 X3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 150</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 700</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Road</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>망치 400</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>망치 1000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>망치 500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>골드 300</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -190,82 +119,14 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>망치 300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>망치 700</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 150</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>나무 250</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>철 500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>망치 600</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>망치 900</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>망치 1500</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>골드 5000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>골드 3000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>골드 200</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>골드 10000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>레벨에 도달 시 건축 가능 건물</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>다음 레벨로 업그레이드 시 필요 재화</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>궁수 X2, 화살공장 X 2, 도로 X 10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>골드 2000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>냉기 제련소 X 3, 화력 제련소 X 3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>돌 공장 X 2, 도로 X 10, 새총 X 2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Mine</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -280,6 +141,39 @@
   <si>
     <t>골드 100</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>골드 400</t>
+  </si>
+  <si>
+    <t>골드 500</t>
+  </si>
+  <si>
+    <t>골드 1000</t>
+  </si>
+  <si>
+    <t>골드 300</t>
+  </si>
+  <si>
+    <t>골드 600</t>
+  </si>
+  <si>
+    <t>골드 900</t>
+  </si>
+  <si>
+    <t>골드 1500</t>
+  </si>
+  <si>
+    <t>골드 100</t>
+  </si>
+  <si>
+    <t>골드 200</t>
+  </si>
+  <si>
+    <t>골드 150</t>
+  </si>
+  <si>
+    <t>골드 250</t>
   </si>
 </sst>
 </file>
@@ -605,7 +499,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="3" max="3" width="12.5" customWidth="1"/>
@@ -618,21 +512,21 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="E2" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -646,7 +540,7 @@
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
@@ -660,10 +554,10 @@
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
@@ -677,10 +571,10 @@
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
@@ -695,17 +589,8 @@
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9" t="s">
-        <v>4</v>
-      </c>
-      <c r="D9" t="s">
-        <v>29</v>
+      <c r="E9" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
@@ -713,33 +598,31 @@
         <v>2</v>
       </c>
       <c r="B10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
       </c>
       <c r="D10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E10" t="s">
-        <v>17</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="E10" s="1"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>2</v>
       </c>
       <c r="B11">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
-      </c>
-      <c r="E11" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="E11" s="1">
+        <v>0.1</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
@@ -747,44 +630,32 @@
         <v>2</v>
       </c>
       <c r="B12">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
       </c>
-      <c r="D12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15" t="s">
-        <v>5</v>
-      </c>
-      <c r="D15" t="s">
-        <v>33</v>
+      <c r="D12" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="1">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>2</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
-        <v>2</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D16" t="s">
-        <v>35</v>
-      </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.3">
@@ -792,16 +663,13 @@
         <v>2</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C17" t="s">
         <v>5</v>
       </c>
       <c r="D17" t="s">
-        <v>34</v>
-      </c>
-      <c r="E17" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.3">
@@ -809,572 +677,280 @@
         <v>2</v>
       </c>
       <c r="B18">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C18" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E21" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" t="s">
-        <v>2</v>
-      </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-      <c r="C22" t="s">
-        <v>6</v>
-      </c>
-      <c r="D22" t="s">
-        <v>36</v>
-      </c>
-      <c r="E22" s="1"/>
+      <c r="D18" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B19">
+        <v>2</v>
+      </c>
+      <c r="C19" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>2</v>
+      </c>
+      <c r="B20">
+        <v>3</v>
+      </c>
+      <c r="C20" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>2</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" t="s">
-        <v>37</v>
-      </c>
-      <c r="E23" s="1">
-        <v>0.1</v>
+      <c r="E23" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B24">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C24" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
-      </c>
-      <c r="E24" s="1">
-        <v>0.1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" t="s">
+        <v>38</v>
+      </c>
+      <c r="E25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26">
+        <v>2</v>
+      </c>
+      <c r="C26" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B27">
         <v>3</v>
       </c>
-      <c r="C25" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E28" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>2</v>
-      </c>
-      <c r="B29">
-        <v>0</v>
-      </c>
-      <c r="C29" t="s">
+      <c r="C27" t="s">
         <v>7</v>
       </c>
-      <c r="D29" t="s">
-        <v>39</v>
+      <c r="D27">
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D30" t="s">
-        <v>38</v>
-      </c>
-      <c r="E30">
-        <v>10</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B31">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D31" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E31">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B32">
+        <v>2</v>
+      </c>
+      <c r="C32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E32">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>6</v>
+      </c>
+      <c r="B33">
         <v>3</v>
       </c>
-      <c r="C32" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E35" t="s">
-        <v>20</v>
+      <c r="C33" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33">
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B36">
         <v>0</v>
       </c>
       <c r="C36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D36" t="s">
-        <v>41</v>
-      </c>
-      <c r="E36" s="1"/>
+        <v>33</v>
+      </c>
+      <c r="E36">
+        <v>20</v>
+      </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B37">
         <v>1</v>
       </c>
       <c r="C37" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D37" t="s">
-        <v>35</v>
-      </c>
-      <c r="E37" s="1">
-        <v>0.1</v>
+        <v>34</v>
+      </c>
+      <c r="E37">
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B38">
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>42</v>
-      </c>
-      <c r="E38" s="1">
-        <v>0.1</v>
+        <v>35</v>
+      </c>
+      <c r="E38">
+        <v>30</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B39">
         <v>3</v>
       </c>
       <c r="C39" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" t="s">
         <v>9</v>
       </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-      <c r="C42" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" t="s">
-        <v>39</v>
-      </c>
-      <c r="E42" s="1"/>
+      <c r="D39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41">
+        <v>0</v>
+      </c>
+      <c r="C41" t="s">
+        <v>17</v>
+      </c>
+      <c r="D41" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C43" t="s">
-        <v>9</v>
+        <v>26</v>
       </c>
       <c r="D43" t="s">
-        <v>38</v>
-      </c>
-      <c r="E43" s="1">
-        <v>0.1</v>
+        <v>28</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B44">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C44" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D44" t="s">
-        <v>40</v>
-      </c>
-      <c r="E44" s="1">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" t="s">
-        <v>9</v>
-      </c>
-      <c r="B45">
-        <v>3</v>
-      </c>
-      <c r="C45" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E48" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" t="s">
-        <v>10</v>
-      </c>
-      <c r="B49">
-        <v>0</v>
-      </c>
-      <c r="C49" t="s">
-        <v>11</v>
-      </c>
-      <c r="D49" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A50" t="s">
-        <v>10</v>
-      </c>
-      <c r="B50">
-        <v>1</v>
-      </c>
-      <c r="C50" t="s">
-        <v>11</v>
-      </c>
-      <c r="D50" t="s">
-        <v>43</v>
-      </c>
-      <c r="E50">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>10</v>
-      </c>
-      <c r="B51">
-        <v>2</v>
-      </c>
-      <c r="C51" t="s">
-        <v>11</v>
-      </c>
-      <c r="D51" t="s">
-        <v>44</v>
-      </c>
-      <c r="E51">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
-        <v>10</v>
-      </c>
-      <c r="B52">
-        <v>3</v>
-      </c>
-      <c r="C52" t="s">
-        <v>11</v>
-      </c>
-      <c r="D52">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A55" t="s">
-        <v>10</v>
-      </c>
-      <c r="B55">
-        <v>0</v>
-      </c>
-      <c r="C55" t="s">
-        <v>12</v>
-      </c>
-      <c r="D55" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>10</v>
-      </c>
-      <c r="B56">
-        <v>1</v>
-      </c>
-      <c r="C56" t="s">
-        <v>12</v>
-      </c>
-      <c r="D56" t="s">
-        <v>30</v>
-      </c>
-      <c r="E56">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A57" t="s">
-        <v>10</v>
-      </c>
-      <c r="B57">
-        <v>2</v>
-      </c>
-      <c r="C57" t="s">
-        <v>12</v>
-      </c>
-      <c r="D57" t="s">
-        <v>46</v>
-      </c>
-      <c r="E57">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A58" t="s">
-        <v>10</v>
-      </c>
-      <c r="B58">
-        <v>3</v>
-      </c>
-      <c r="C58" t="s">
-        <v>12</v>
-      </c>
-      <c r="D58">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A61" t="s">
-        <v>10</v>
-      </c>
-      <c r="B61">
-        <v>0</v>
-      </c>
-      <c r="C61" t="s">
-        <v>13</v>
-      </c>
-      <c r="D61" t="s">
-        <v>47</v>
-      </c>
-      <c r="E61">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A62" t="s">
-        <v>10</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="C62" t="s">
-        <v>13</v>
-      </c>
-      <c r="D62" t="s">
-        <v>48</v>
-      </c>
-      <c r="E62">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A63" t="s">
-        <v>10</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
-      </c>
-      <c r="C63" t="s">
-        <v>13</v>
-      </c>
-      <c r="D63" t="s">
-        <v>49</v>
-      </c>
-      <c r="E63">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>10</v>
-      </c>
-      <c r="B64">
-        <v>3</v>
-      </c>
-      <c r="C64" t="s">
-        <v>13</v>
-      </c>
-      <c r="D64">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E66" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A67" t="s">
         <v>23</v>
-      </c>
-      <c r="B67">
-        <v>1</v>
-      </c>
-      <c r="D67" t="s">
-        <v>57</v>
-      </c>
-      <c r="E67" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" t="s">
-        <v>22</v>
-      </c>
-      <c r="B68">
-        <v>2</v>
-      </c>
-      <c r="D68" t="s">
-        <v>51</v>
-      </c>
-      <c r="E68" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>22</v>
-      </c>
-      <c r="B69">
-        <v>3</v>
-      </c>
-      <c r="D69" t="s">
-        <v>50</v>
-      </c>
-      <c r="E69" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A70" t="s">
-        <v>22</v>
-      </c>
-      <c r="B70">
-        <v>4</v>
-      </c>
-      <c r="D70" t="s">
-        <v>53</v>
-      </c>
-      <c r="E70" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A71" t="s">
-        <v>22</v>
-      </c>
-      <c r="B71">
-        <v>5</v>
-      </c>
-      <c r="E71" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A73" t="s">
-        <v>32</v>
-      </c>
-      <c r="B73">
-        <v>0</v>
-      </c>
-      <c r="C73" t="s">
-        <v>32</v>
-      </c>
-      <c r="D73" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A75" t="s">
-        <v>60</v>
-      </c>
-      <c r="B75">
-        <v>0</v>
-      </c>
-      <c r="C75" t="s">
-        <v>61</v>
-      </c>
-      <c r="D75" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A76" t="s">
-        <v>60</v>
-      </c>
-      <c r="B76">
-        <v>0</v>
-      </c>
-      <c r="C76" t="s">
-        <v>62</v>
-      </c>
-      <c r="D76" t="s">
-        <v>52</v>
       </c>
     </row>
   </sheetData>
